--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3080,12 +3080,12 @@
       <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>添祥、海大</t>
+          <t>唐人神（小料）、天翔819（大料）</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>添祥、郑海杰</t>
+          <t>原添祥、郑海杰，现待问清</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3093,12 +3093,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>跟添祥、郑海杰拿料，鱼苗和大头混养，宝路苗，大鱼七八两。 【名字确认：名单原"施军华""司君华"均为同一人施君华；10.05客情维护走访】</t>
+          <t>10.09走访：用料已更换，现小料唐人神、大料天翔819（挂账价114，属低档料，判断难养出效果）；现跟谁拿料待问清。鱼苗和大头混养，宝路苗，鱼现八两左右，预计11月初出鱼。【名字确认：名单原“施军华”“司君华”均为同一人施君华；10.05客情维护走访】</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>持续服务培育，寻找切入时机</t>
+          <t>11月初出鱼后回访，核实天翔819这造包产；问清现拿料对象；持续服务培育，寻找切入时机</t>
         </is>
       </c>
     </row>
@@ -4201,6 +4201,141 @@
       <c r="L99" t="inlineStr">
         <is>
           <t>【10.08走访，交谈养殖情况：现金料用户，现用歌颂和璃元（本地料），包产43左右，跟陈儒和三弟拿料；对通威印象最近变差，认为价格偏高】</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>王森飞</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>10.09走访不在家，未交谈。</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>换个时间点再访</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>朱肖水</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>10.09走访不在家，未交谈。</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>换个时间点再访</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>潘如军</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>10.09走访不在家，未交谈。</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>再约时间回访</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>郑康强</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>祥泰</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>田永均</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>10.09拜访：跟田永均拿料，田永均不拉通威、用户也没法拉；本人之前用过通威但用得少；聊天意愿低。</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>保持客情，择机再访</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>朱耀武</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>10.09拜访：用户不愿意交谈。</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>暂缓密集跟进，择机再接触</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4396,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
@@ -4271,7 +4406,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>丁志杰</t>
+          <t>丁志开</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1360,19 +1360,27 @@
         <v>7</v>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>海大2552、混渝泰/粤海</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>周公宝</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>七口塘，计划安装料塔，对通威认可度较高。</t>
+          <t>七口塘，计划安装料塔，对通威认可度较高；老婆湖南人（同乡圈）；主用海大2552、偶尔混渝泰、粤海；跟周公宝拿料；主动问价，转化机会明确。与唐行平（湖南老乡）互相认识，可借同乡关系交叉跟进。10.10客情走访。</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>持续服务培育，寻找切入时机</t>
+          <t>趁其主动询价推通威小料/开口乐报价；借同乡关系（唐行平）交叉跟进。</t>
         </is>
       </c>
     </row>
@@ -1999,19 +2007,27 @@
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>翔泰、通威</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>马津深</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>5口在养鱼塘多处亚盐偏高，已推荐降亚盐动保。</t>
+          <t>5口在养鱼塘多处亚盐偏高；基本全程用翔泰、拉过一车通威；反映翔泰长得不行，后两月冲重量想拉通威，但经销商马津深（同音，马金生即马津深、已并）不给拉；准备拿苗原13号推迟至16号；其弟丁开福苗塘已放60万苗（约4800尾/斤），趁早刺激快速转料，便于后续用通威小料'开口乐'开口。10.10客情走访。</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>持续服务培育，寻找切入时机</t>
+          <t>盯紧拿苗节点（16号），拿苗后趁冲重量需求推通威；借丁开福放苗刺激快速转料、推开口乐；渠道被马津深卡不给拉，需先打通通路。</t>
         </is>
       </c>
     </row>
@@ -4336,6 +4352,79 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>暂缓密集跟进，择机再接触</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>陈浩成</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>二、高意向客户</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>通威（本兆前段用一点翔泰、后转通威）</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>—（公司饲料活动拿料）</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>8月即作为通威用户参加公司饲料活动拿料；本兆前面用过一点翔泰、后面才转用通威；上次活动拉了一点通威用到现在，下一兆提了一嘴要用全程通威。测水：14:20塘亚盐0.15、14:23塘亚盐0.10，pH均7.4。塘口位置待确认。10.10新增用户走访。</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>加强拜访频次、做好客情服务，趁其提全程通威趁热打铁促转。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>陈南高</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>百洋（最低端）</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>—（百洋直供，不经经销商）</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>百洋直供用户，直接从厂里拿料，不经经销商；用百洋最低端料，包产不高；因直供价低转料意愿不强。其租的塘明年5月到期，届时需另找养户租塘续养、不找经销商（找经销商租塘就被绑定按经销商意思拿料、比百洋直供贵、不划算）。10.10客情走访。</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>转化机会低，维持正常客勤，不单列高价值跟进。</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4475,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -4396,7 +4485,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -4406,7 +4495,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>二、高意向客户</t>
+          <t>一、通威现有用户</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -4425,6 +4425,31 @@
       <c r="M106" t="inlineStr">
         <is>
           <t>转化机会低，维持正常客勤，不单列高价值跟进。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>唐行平</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>10.10抓鱼（出鱼期），未拜访、未交谈；养殖规模、现用料、拿料对象、地址等待出鱼后回访补全；与宋平（湖南老乡）互相认识，可借同乡关系交叉跟进。</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>出鱼后回访，补建档案信息；借宋平同乡关系搭桥。</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4490,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -4475,7 +4500,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4485,7 +4510,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
@@ -4495,7 +4520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -4444,12 +4444,13 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>10.10抓鱼（出鱼期），未拜访、未交谈；养殖规模、现用料、拿料对象、地址等待出鱼后回访补全；与宋平（湖南老乡）互相认识，可借同乡关系交叉跟进。</t>
+          <t>【养殖关键节点】出鱼/抓鱼：2026-10-10（出鱼期，抓鱼中）；放苗时间：待出鱼后回访补全。
+— 10.10抓鱼（出鱼期），未拜访、未交谈；养殖规模、现用料、拿料对象、地址等待出鱼后回访补全；与宋平（湖南老乡）互相认识，可借同乡关系交叉跟进。</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>出鱼后回访，补建档案信息；借宋平同乡关系搭桥。</t>
+          <t>出鱼（10.10抓鱼）后回访，补全放苗/养殖周期节点与档案信息；借宋平同乡关系搭桥。</t>
         </is>
       </c>
     </row>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -2104,12 +2104,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>原用通威9911，后被百洋切走，现用百洋，存鱼五两左右。</t>
+          <t>原用通威9911，后被百洋切走，现用百洋，存鱼五两左右。【养殖关键节点】放苗：近期新抓60万尾苗放入（约10.10前后，与丁志开拿苗节点同期），平均4800尾/斤（约125斤）。</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>持续服务培育，寻找切入时机</t>
+          <t>持续服务培育，寻找切入时机；借其放苗（60万尾）刺激兄长丁志开快速转料、推通威开口乐。</t>
         </is>
       </c>
     </row>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -2104,7 +2104,7 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>原用通威9911，后被百洋切走，现用百洋，存鱼五两左右。【养殖关键节点】放苗：近期新抓60万尾苗放入（约10.10前后，与丁志开拿苗节点同期），平均4800尾/斤（约125斤）。</t>
+          <t>原用通威9911，后被百洋切走，现用百洋，存鱼五两左右。【养殖关键节点】放苗：9月16日新抓60万尾苗放入，平均4800尾/斤（约125斤）。</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4451,6 +4451,41 @@
       <c r="M107" t="inlineStr">
         <is>
           <t>出鱼（10.10抓鱼）后回访，补全放苗/养殖周期节点与档案信息；借宋平同乡关系搭桥。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>黄少雄</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>翔泰</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>稳定且较高（陈南高亲述）</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>陈南高亲述翔泰高产样板用户（陈南高聊天中作'黄绍雄'，同音确认同一人，电话13036004961）；现用翔泰料，包产稳定且较高；可作翔泰高产样板/转介绍突破点。</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>作为翔泰高产样板用户经营客情，借其高产口碑做转介绍突破；择机推介通威。</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4546,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -4521,7 +4556,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>黄少雄</t>
+          <t>黄绍雄</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>陈南高亲述翔泰高产样板用户（陈南高聊天中作'黄绍雄'，同音确认同一人，电话13036004961）；现用翔泰料，包产稳定且较高；可作翔泰高产样板/转介绍突破点。</t>
+          <t>陈南高亲述翔泰高产样板用户（陈南高聊天中提及，电话13036004961）；现用翔泰料，包产稳定且较高；可作翔泰高产样板/转介绍突破点。</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -1157,7 +1157,11 @@
           <t>祥泰</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>田永均</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -4348,6 +4348,11 @@
           <t>三、潜力培育中</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>田永均</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>10.09拜访：用户不愿意交谈。</t>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>周公保</t>
+          <t>周公宝</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3434,7 +3434,7 @@
       <c r="G78" s="3" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>周公保</t>
+          <t>周公宝</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>

--- a/数据/用户摸牌表.xlsx
+++ b/数据/用户摸牌表.xlsx
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>周公宝</t>
+          <t>周公保</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3434,7 +3434,7 @@
       <c r="G78" s="3" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>周公宝</t>
+          <t>周公保</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4051,6 +4051,11 @@
       <c r="C94" t="inlineStr">
         <is>
           <t>三、潜力培育中</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>锦山</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
